--- a/data/trans_orig/P1420-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2012</t>
+          <t>Población con diagnóstico de hemorroides en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429273</t>
+          <t>428747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436328</t>
+          <t>436319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304389</t>
+          <t>305192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313373</t>
+          <t>313472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737989</t>
+          <t>738438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748653</t>
+          <t>748757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411448</t>
+          <t>411259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324719</t>
+          <t>325200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335915</t>
+          <t>335764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741117</t>
+          <t>740491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752855</t>
+          <t>753531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619262</t>
+          <t>618844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628395</t>
+          <t>628450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250422</t>
+          <t>250333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259136</t>
+          <t>259165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874640</t>
+          <t>874897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>885709</t>
+          <t>885865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1137697</t>
+          <t>1138374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1152140</t>
+          <t>1152022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748718</t>
+          <t>748490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761601</t>
+          <t>761604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892675</t>
+          <t>1891764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1911234</t>
+          <t>1911465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32738</t>
+          <t>32303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499259</t>
+          <t>497208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508507</t>
+          <t>508425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734567</t>
+          <t>734236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>750606</t>
+          <t>751349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1238105</t>
+          <t>1238540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256931</t>
+          <t>1257266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>27540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1083606</t>
+          <t>1081811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1099889</t>
+          <t>1097996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1349293</t>
+          <t>1349022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1365823</t>
+          <t>1365791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>39105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42282</t>
+          <t>42967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73006</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>82788</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>66892</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>102170</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>82788</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>65334</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>101902</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3382587</t>
+          <t>3382805</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3403511</t>
+          <t>3403768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3473909</t>
+          <t>3474579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3504633</t>
+          <t>3503948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,47 +2952,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6886037</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6866655</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6901933</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>98,81%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6886037</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6866923</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6903491</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2016</t>
+          <t>Población con diagnóstico de hemorroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408542</t>
+          <t>406941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424749</t>
+          <t>424557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>347055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754615</t>
+          <t>754413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771358</t>
+          <t>771178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365764</t>
+          <t>365923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376197</t>
+          <t>376259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364828</t>
+          <t>365363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736466</t>
+          <t>735857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746986</t>
+          <t>747295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515890</t>
+          <t>516142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160263</t>
+          <t>160343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679708</t>
+          <t>680367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687253</t>
+          <t>687245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133162</t>
+          <t>1133687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145950</t>
+          <t>1145770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>807424</t>
+          <t>808339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820804</t>
+          <t>820930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945748</t>
+          <t>1946599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963923</t>
+          <t>1964262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604374</t>
+          <t>604186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616929</t>
+          <t>616953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715747</t>
+          <t>715867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731745</t>
+          <t>731931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1325648</t>
+          <t>1326990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1346130</t>
+          <t>1346319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1051572</t>
+          <t>1050441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071059</t>
+          <t>1070866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337989</t>
+          <t>1338656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357984</t>
+          <t>1358130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>47566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63048</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62631</t>
+          <t>63009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102131</t>
+          <t>100411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3337321</t>
+          <t>3338156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3362527</t>
+          <t>3362004</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3468548</t>
+          <t>3470114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3498591</t>
+          <t>3497569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6815187</t>
+          <t>6816907</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6854687</t>
+          <t>6854309</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P1420-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428747</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436319</t>
+          <t>436336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305192</t>
+          <t>304247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313472</t>
+          <t>313449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738438</t>
+          <t>738165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748757</t>
+          <t>748728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411259</t>
+          <t>411794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325200</t>
+          <t>324945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335764</t>
+          <t>335151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740491</t>
+          <t>740900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753531</t>
+          <t>753545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618844</t>
+          <t>619903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628450</t>
+          <t>628394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250333</t>
+          <t>250373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259165</t>
+          <t>259167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874897</t>
+          <t>874473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>885865</t>
+          <t>885739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138374</t>
+          <t>1137074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1152022</t>
+          <t>1152037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748490</t>
+          <t>748147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761604</t>
+          <t>761582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1891764</t>
+          <t>1892627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1911465</t>
+          <t>1911390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26010</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32303</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497208</t>
+          <t>498078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508425</t>
+          <t>508461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734236</t>
+          <t>734099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>751349</t>
+          <t>750602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1238540</t>
+          <t>1237046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257266</t>
+          <t>1256744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>27361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1081811</t>
+          <t>1081990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1097996</t>
+          <t>1099002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1349022</t>
+          <t>1348436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1365791</t>
+          <t>1365530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39105</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42967</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72336</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102170</t>
+          <t>102209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3382805</t>
+          <t>3383321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3403768</t>
+          <t>3403830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3474579</t>
+          <t>3472863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3503948</t>
+          <t>3504452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6866655</t>
+          <t>6866616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6901933</t>
+          <t>6902719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406941</t>
+          <t>407214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424557</t>
+          <t>424265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754413</t>
+          <t>755076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771178</t>
+          <t>770880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365923</t>
+          <t>366710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376259</t>
+          <t>376130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365363</t>
+          <t>365402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735857</t>
+          <t>735432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747295</t>
+          <t>746625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516142</t>
+          <t>515069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>160865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>680367</t>
+          <t>680019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687245</t>
+          <t>687250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133687</t>
+          <t>1132922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145770</t>
+          <t>1145749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808339</t>
+          <t>807900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820930</t>
+          <t>820998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946599</t>
+          <t>1945752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964262</t>
+          <t>1963957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604186</t>
+          <t>605375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616953</t>
+          <t>616834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715867</t>
+          <t>715655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731931</t>
+          <t>731585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1326990</t>
+          <t>1325463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1346319</t>
+          <t>1345784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1050441</t>
+          <t>1050869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1070866</t>
+          <t>1070616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1338656</t>
+          <t>1338288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1358130</t>
+          <t>1358062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>22294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47566</t>
+          <t>47002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>63389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63009</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100411</t>
+          <t>102341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3338156</t>
+          <t>3338720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3362004</t>
+          <t>3363428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470114</t>
+          <t>3468207</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3497569</t>
+          <t>3497596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6816907</t>
+          <t>6814977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6854309</t>
+          <t>6854339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
